--- a/data_src/levels/ch1_l01/热点表.xlsx
+++ b/data_src/levels/ch1_l01/热点表.xlsx
@@ -813,47 +813,33 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>collect</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>723</v>
+      </c>
+      <c r="G4" t="n">
+        <v>163</v>
+      </c>
+      <c r="H4" t="n">
+        <v>75</v>
+      </c>
+      <c r="I4" t="n">
+        <v>54</v>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>vocab_aroz</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr">
         <is>
           <t>1</t>
@@ -869,16 +855,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -896,35 +877,23 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>603</v>
+      </c>
+      <c r="G5" t="n">
+        <v>112</v>
+      </c>
+      <c r="H5" t="n">
+        <v>75</v>
+      </c>
+      <c r="I5" t="n">
+        <v>110</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>modal_102</t>
@@ -970,8 +939,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>296</t>
@@ -999,40 +966,28 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>686</v>
+      </c>
+      <c r="G6" t="n">
+        <v>360</v>
+      </c>
+      <c r="H6" t="n">
+        <v>93</v>
+      </c>
+      <c r="I6" t="n">
+        <v>206</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>vocab_americano</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>americano_icon_unlocked</t>
@@ -1043,7 +998,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1059,16 +1013,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1086,40 +1035,28 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>843</v>
+      </c>
+      <c r="G7" t="n">
+        <v>238</v>
+      </c>
+      <c r="H7" t="n">
+        <v>31</v>
+      </c>
+      <c r="I7" t="n">
+        <v>47</v>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>vocab_apple_latte</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>apple_latte_icon_unlocked</t>
@@ -1130,7 +1067,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1146,16 +1082,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1173,41 +1104,28 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>463</v>
+      </c>
+      <c r="G8" t="n">
+        <v>341</v>
+      </c>
+      <c r="H8" t="n">
+        <v>51</v>
+      </c>
+      <c r="I8" t="n">
+        <v>66</v>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>modal_105</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>15</t>
@@ -1243,17 +1161,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
+      <c r="X8" t="n">
+        <v>456</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1272,47 +1184,33 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
+      <c r="F9" t="n">
+        <v>112</v>
+      </c>
+      <c r="G9" t="n">
+        <v>394</v>
+      </c>
+      <c r="H9" t="n">
+        <v>294</v>
+      </c>
+      <c r="I9" t="n">
+        <v>188</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>使用痕迹很重的专业化妆刷</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>0</t>
@@ -1328,16 +1226,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1347,7 +1240,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>手机</t>
+          <t>手机 anchor=492,15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1355,41 +1248,28 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>533</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>557</v>
+      </c>
+      <c r="G10" t="n">
+        <v>435</v>
+      </c>
+      <c r="H10" t="n">
+        <v>115</v>
+      </c>
+      <c r="I10" t="n">
+        <v>111</v>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>modal_107</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1425,17 +1305,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
+      <c r="X10" t="n">
+        <v>297</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>567</v>
       </c>
     </row>
     <row r="11">
@@ -1454,7 +1328,6 @@
           <t>modal_107</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>modal</t>
@@ -1480,15 +1353,11 @@
           <t>78</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>panel_phone_p</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>20</t>
@@ -1524,7 +1393,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
           <t>hidden</t>
@@ -1557,7 +1425,6 @@
           <t>modal_107</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>modal</t>
@@ -1583,15 +1450,11 @@
           <t>77</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>panel_phone_kkt</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>21</t>
@@ -1627,7 +1490,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
           <t>hidden</t>
@@ -1660,41 +1522,28 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>555</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>513</v>
+      </c>
+      <c r="G13" t="n">
+        <v>341</v>
+      </c>
+      <c r="H13" t="n">
+        <v>51</v>
+      </c>
+      <c r="I13" t="n">
+        <v>66</v>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>modal_108</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>15</t>
@@ -1730,17 +1579,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>684</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
+      <c r="X13" t="n">
+        <v>460</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="14">
@@ -1759,40 +1602,28 @@
           <t>root</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
+      <c r="F14" t="n">
+        <v>320</v>
+      </c>
+      <c r="G14" t="n">
+        <v>152</v>
+      </c>
+      <c r="H14" t="n">
+        <v>71</v>
+      </c>
+      <c r="I14" t="n">
+        <v>147</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>穿着演出服的男人</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>leo_portrait_unlocked</t>
@@ -1803,7 +1634,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
           <t>0</t>
@@ -1819,16 +1649,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1846,43 +1671,28 @@
           <t>modal_105</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>405</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>47</v>
+      </c>
+      <c r="I15" t="n">
+        <v>47</v>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
           <t>0</t>
@@ -1898,20 +1708,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1929,43 +1735,28 @@
           <t>modal_108</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>408</v>
+      </c>
+      <c r="G16" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>47</v>
+      </c>
+      <c r="I16" t="n">
+        <v>48</v>
+      </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
           <t>0</t>
@@ -1981,20 +1772,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2012,41 +1799,28 @@
           <t>modal_108</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>148</v>
+      </c>
+      <c r="G17" t="n">
+        <v>248</v>
+      </c>
+      <c r="H17" t="n">
+        <v>69</v>
+      </c>
+      <c r="I17" t="n">
+        <v>79</v>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>panel_201</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>10</t>
@@ -2072,27 +1846,21 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+      <c r="X17" t="n">
+        <v>195</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>316</v>
       </c>
     </row>
     <row r="18">
@@ -2103,7 +1871,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>购物小票</t>
+          <t>购物小票 anchor=499,53</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2111,35 +1879,23 @@
           <t>modal_108</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>204</v>
+      </c>
+      <c r="G18" t="n">
+        <v>276</v>
+      </c>
+      <c r="H18" t="n">
+        <v>63</v>
+      </c>
+      <c r="I18" t="n">
+        <v>58</v>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>panel_206</t>
@@ -2185,21 +1941,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
+      <c r="X18" t="n">
+        <v>284</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>515</v>
       </c>
     </row>
     <row r="19">
@@ -2218,47 +1969,33 @@
           <t>panel_206</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>collect</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>22</v>
+      </c>
+      <c r="G19" t="n">
+        <v>219</v>
+      </c>
+      <c r="H19" t="n">
+        <v>66</v>
+      </c>
+      <c r="I19" t="n">
+        <v>34</v>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>vocab_americano</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr">
         <is>
           <t>1</t>
@@ -2274,20 +2011,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2305,47 +2038,33 @@
           <t>panel_206</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>collect</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>22</v>
+      </c>
+      <c r="G20" t="n">
+        <v>268</v>
+      </c>
+      <c r="H20" t="n">
+        <v>71</v>
+      </c>
+      <c r="I20" t="n">
+        <v>37</v>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>vocab_apple_latte</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr">
         <is>
           <t>1</t>
@@ -2361,20 +2080,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2384,7 +2099,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>工作证按钮</t>
+          <t>工作证按钮 anchor=503,18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2392,41 +2107,28 @@
           <t>modal_105</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>228</v>
+      </c>
+      <c r="G21" t="n">
+        <v>258</v>
+      </c>
+      <c r="H21" t="n">
+        <v>67</v>
+      </c>
+      <c r="I21" t="n">
+        <v>84</v>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>panel_205</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>10</t>
@@ -2462,21 +2164,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>486</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
+      <c r="X21" t="n">
+        <v>380</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>480</v>
       </c>
     </row>
     <row r="22">
@@ -2495,41 +2192,28 @@
           <t>modal_105</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>140</v>
+      </c>
+      <c r="G22" t="n">
+        <v>271</v>
+      </c>
+      <c r="H22" t="n">
+        <v>41</v>
+      </c>
+      <c r="I22" t="n">
+        <v>57</v>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>panel_207</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>10</t>
@@ -2565,21 +2249,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+      <c r="X22" t="n">
+        <v>195</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>316</v>
       </c>
     </row>
     <row r="23">
@@ -2598,41 +2277,28 @@
           <t>modal_105</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>modal</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>177</v>
+      </c>
+      <c r="G23" t="n">
+        <v>271</v>
+      </c>
+      <c r="H23" t="n">
+        <v>43</v>
+      </c>
+      <c r="I23" t="n">
+        <v>59</v>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>panel_208</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>10</t>
@@ -2668,21 +2334,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
           <t>hidden</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+      <c r="X23" t="n">
+        <v>195</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>316</v>
       </c>
     </row>
     <row r="24">
@@ -2701,47 +2362,33 @@
           <t>panel_208</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>collect</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>59</v>
+      </c>
+      <c r="G24" t="n">
+        <v>140</v>
+      </c>
+      <c r="H24" t="n">
+        <v>160</v>
+      </c>
+      <c r="I24" t="n">
+        <v>146</v>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>vocab_keycard</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
           <t>1</t>
@@ -2757,16 +2404,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2784,47 +2426,33 @@
           <t>panel_205</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>collect</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>88</v>
+      </c>
+      <c r="G25" t="n">
+        <v>248</v>
+      </c>
+      <c r="H25" t="n">
+        <v>99</v>
+      </c>
+      <c r="I25" t="n">
+        <v>24</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>vocab_hzs</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr">
         <is>
           <t>1</t>
@@ -2840,16 +2468,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2867,47 +2490,33 @@
           <t>panel_205</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>collect</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>186</v>
+      </c>
+      <c r="G26" t="n">
+        <v>251</v>
+      </c>
+      <c r="H26" t="n">
+        <v>48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>25</v>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>vocab_may</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr">
         <is>
           <t>1</t>
@@ -2923,16 +2532,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2950,47 +2554,33 @@
           <t>panel_201</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>collect</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>66</v>
+      </c>
+      <c r="G27" t="n">
+        <v>215</v>
+      </c>
+      <c r="H27" t="n">
+        <v>73</v>
+      </c>
+      <c r="I27" t="n">
+        <v>38</v>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>vocab_leo</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
           <t>1</t>
@@ -3006,16 +2596,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3033,7 +2618,6 @@
           <t>panel_phone_p</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>collect</t>
@@ -3059,21 +2643,16 @@
           <t>20</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>vocab_qrj</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
           <t>1</t>
@@ -3089,16 +2668,11 @@
           <t>0</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
